--- a/94_SNP_Simulation/94_SNP_Comparison/Outputs/Comparison/Summary_Stats_Comparison.xlsx
+++ b/94_SNP_Simulation/94_SNP_Comparison/Outputs/Comparison/Summary_Stats_Comparison.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huncho/Desktop/Forensic_Kinship/94_SNP_Simulation/Comparison/Outputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huncho/Desktop/Forensic_Kinship/94_SNP_Simulation/94_SNP_Comparison/Outputs/Comparison/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995F559D-5154-B04C-B413-057DEDF670E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C5A4B8-73B2-034C-ADD0-62CB80C2FEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6040" yWindow="540" windowWidth="15940" windowHeight="16300" xr2:uid="{951F29B7-278F-3C4D-9B95-944C38ABA707}"/>
+    <workbookView xWindow="5100" yWindow="500" windowWidth="23080" windowHeight="16160" xr2:uid="{951F29B7-278F-3C4D-9B95-944C38ABA707}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -68,10 +68,10 @@
     <t>HS</t>
   </si>
   <si>
-    <t xml:space="preserve">LUCINDA'S RESULTS </t>
-  </si>
-  <si>
-    <t>MY RESULTS</t>
+    <t>MERLIN</t>
+  </si>
+  <si>
+    <t>FamLink</t>
   </si>
 </sst>
 </file>
@@ -500,7 +500,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K1" s="2"/>
     </row>
@@ -764,7 +764,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
